--- a/static/prediction_history.xlsx
+++ b/static/prediction_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,6 +599,201 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>2026-02-07 21:31:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F5" t="n">
+        <v>40</v>
+      </c>
+      <c r="G5" t="n">
+        <v>25</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>No Churn</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>13</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-02-07 21:51:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>No Churn</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>33</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-02-10 19:10:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>20</v>
+      </c>
+      <c r="E7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>No Churn</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>36</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-02-11 11:41:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E8" t="n">
+        <v>25</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>No Churn</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>36</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-02-11 11:42:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>200</v>
+      </c>
+      <c r="F9" t="n">
+        <v>50</v>
+      </c>
+      <c r="G9" t="n">
+        <v>90</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>No Churn</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>44</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-03-08 16:36:21</t>
         </is>
       </c>
     </row>
